--- a/reports/pdf_rolling5_20260728.xlsx
+++ b/reports/pdf_rolling5_20260728.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,032억   ·   현금 48억(1.2%)      오늘 2026-07-28  vs  5일전 2026-07-21      매수 16종목  /  매도 20종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,141억   ·   현금 48억(1.2%)      오늘 2026-07-28  vs  5일전 2026-07-21      매수 16종목  /  매도 20종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>321</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1426260780</v>
+        <v>1423391040</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-42</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-548151240</v>
+        <v>-547048320</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>40</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1043700000</v>
+        <v>1041600000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-41</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1230770800</v>
+        <v>-1228294400</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>38</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1099165200</v>
+        <v>1096953600</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-26</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-464416680</v>
+        <v>-463482240</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>31</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1343490400</v>
+        <v>1340787200</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-25</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-408037000</v>
+        <v>-407216000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>29</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1617138600</v>
+        <v>1613884800</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -855,23 +855,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>코오롱생명과학  (편출)</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-23</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-688146200</v>
+        <v>-908076800</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.16%→0.00%</t>
+          <t>1.05%→0.94%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>23→0</t>
+          <t>121→98</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
         <v>23</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>339272080</v>
+        <v>338589440</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -899,23 +899,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>코오롱생명과학  (편출)</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-23</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-909907600</v>
+        <v>-686761600</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>1.05%→0.94%</t>
+          <t>0.16%→0.00%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>121→98</t>
+          <t>23→0</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1773296000</v>
+        <v>1769728000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-20</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-460222000</v>
+        <v>-459296000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -966,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1100954400</v>
+        <v>403545600</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>3.97%→4.00%</t>
+          <t>0.68%→0.77%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>168→180</t>
+          <t>82→94</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -994,7 +994,7 @@
         <v>-17</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-669160800</v>
+        <v>-667814400</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>404359200</v>
+        <v>1098739200</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>0.68%→0.77%</t>
+          <t>3.97%→4.00%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>82→94</t>
+          <t>168→180</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1038,7 +1038,7 @@
         <v>-15</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-903546000</v>
+        <v>-901728000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>391238400</v>
+        <v>390451200</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1075,23 +1075,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-372948800</v>
+        <v>-424972800</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.27%</t>
+          <t>0.58%→0.52%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>56→42</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
         <v>9</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>380205000</v>
+        <v>379440000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1119,23 +1119,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-425829600</v>
+        <v>-438860800</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.52%</t>
+          <t>1.03%→0.97%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>142→128</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
         <v>8</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>320465600</v>
+        <v>319820800</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1163,23 +1163,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-439745600</v>
+        <v>-372198400</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.03%→0.97%</t>
+          <t>0.39%→0.27%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>142→128</t>
+          <t>56→42</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
         <v>8</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1598352000</v>
+        <v>1595136000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>-11</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-809116000</v>
+        <v>-807488000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>5</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>725620000</v>
+        <v>724160000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>-8</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-217487200</v>
+        <v>-217049600</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>4</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1773296000</v>
+        <v>1769728000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>-6</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-351876000</v>
+        <v>-351168000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>3</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>623238000</v>
+        <v>621984000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>-6</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-432986400</v>
+        <v>-432115200</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1367,23 +1367,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-706237000</v>
+        <v>-399776000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>9.05%→7.46%</t>
+          <t>0.44%→0.39%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>223→218</t>
+          <t>25→20</t>
         </is>
       </c>
     </row>
@@ -1395,23 +1395,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-400582000</v>
+        <v>-743504000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.39%</t>
+          <t>1.20%→0.90%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>25→20</t>
+          <t>30→25</t>
         </is>
       </c>
     </row>
@@ -1423,23 +1423,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-745003000</v>
+        <v>-704816000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>1.20%→0.90%</t>
+          <t>9.05%→7.46%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>30→25</t>
+          <t>223→218</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
         <v>-3</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-339053400</v>
+        <v>-338371200</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,527억   ·   현금 26억(0.7%)      오늘 2026-07-28  vs  5일전 2026-07-21      매수 5종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,519억   ·   현금 26억(0.7%)      오늘 2026-07-28  vs  5일전 2026-07-21      매수 5종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
@@ -1570,7 +1570,7 @@
         <v>46</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>1813402800</v>
+        <v>1773327600</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>-138</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-7313558400</v>
+        <v>-7151932800</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>40</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1031700000</v>
+        <v>1008900000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>17</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>1049564700</v>
+        <v>1026369900</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>12</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>2032992000</v>
+        <v>1988064000</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>5</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>1060207500</v>
+        <v>1036777500</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,302억   ·   현금 74억(3.1%)      오늘 2026-07-28  vs  5일전 2026-07-21      매수 4종목  /  매도 4종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,359억   ·   현금 74억(3.1%)      오늘 2026-07-28  vs  5일전 2026-07-21      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
@@ -1815,7 +1815,7 @@
         <v>31</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1729031200</v>
+        <v>1724034000</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>-117</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-3028053600</v>
+        <v>-3019302000</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>26</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>426410400</v>
+        <v>425178000</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>-110</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-5107652000</v>
+        <v>-5092890000</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>22</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>4749888000</v>
+        <v>4736160000</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>-49</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-397401760</v>
+        <v>-396253200</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>12</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>3703584000</v>
+        <v>3692880000</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>-30</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-2949996000</v>
+        <v>-2941470000</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
     <row r="44" ht="19" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,238억   ·   현금 16억(0.7%)      오늘 2026-07-28  vs  5일전 2026-07-21      매수 5종목  /  매도 1종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,030억   ·   현금 16억(0.7%)      오늘 2026-07-28  vs  5일전 2026-07-21      매수 5종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B44" s="4" t="n"/>
@@ -2229,7 +2229,7 @@
     <row r="53" ht="19" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 267억   ·   현금 2억(0.6%)      오늘 2026-07-28  vs  5일전 2026-07-21      매수 12종목  /  매도 10종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 271억   ·   현금 2억(0.6%)      오늘 2026-07-28  vs  5일전 2026-07-21      매수 12종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B53" s="4" t="n"/>
@@ -2325,7 +2325,7 @@
         <v>152</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>37601760</v>
+        <v>38006080</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2346,11 +2346,11 @@
         <v>-139</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-40565760</v>
+        <v>-38558600</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>3.01%→2.84%</t>
+          <t>2.83%→2.67%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2369,11 +2369,11 @@
         <v>91</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>51731680</v>
+        <v>49864360</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>7.16%→7.31%</t>
+          <t>6.82%→6.96%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2390,11 +2390,11 @@
         <v>-77</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-87780000</v>
+        <v>-93105320</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.00%</t>
+          <t>0.35%→0.00%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
@@ -2413,11 +2413,11 @@
         <v>49</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>70756000</v>
+        <v>69564320</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>3.12%→3.37%</t>
+          <t>3.03%→3.27%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -2434,11 +2434,11 @@
         <v>-63</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-186732000</v>
+        <v>-190562400</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>8.16%→7.41%</t>
+          <t>8.23%→7.47%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>6.05%→6.31%</t>
+          <t>5.98%→6.23%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
@@ -2478,11 +2478,11 @@
         <v>-11</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-51999200</v>
+        <v>-50661600</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>2.66%→2.45%</t>
+          <t>2.56%→2.35%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -2501,11 +2501,11 @@
         <v>33</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>56304600</v>
+        <v>59439600</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>0.21%→0.42%</t>
+          <t>0.22%→0.44%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -2522,11 +2522,11 @@
         <v>-10</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-61028000</v>
+        <v>-63004000</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>1.20%→0.96%</t>
+          <t>1.22%→0.98%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -2545,11 +2545,11 @@
         <v>27</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>150411600</v>
+        <v>153694800</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>2.96%→3.51%</t>
+          <t>2.99%→3.54%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
@@ -2559,23 +2559,23 @@
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-36236800</v>
+        <v>-39459200</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>0.65%→0.51%</t>
+          <t>1.12%→0.97%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>38→30</t>
+          <t>61→53</t>
         </is>
       </c>
     </row>
@@ -2589,11 +2589,11 @@
         <v>13</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>24354200</v>
+        <v>25688000</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>0.69%→0.78%</t>
+          <t>0.72%→0.81%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
@@ -2603,23 +2603,23 @@
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-39216000</v>
+        <v>-35872000</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>1.13%→0.97%</t>
+          <t>0.63%→0.50%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>61→53</t>
+          <t>38→30</t>
         </is>
       </c>
     </row>
@@ -2633,11 +2633,11 @@
         <v>12</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>124123200</v>
+        <v>129595200</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>2.61%→3.06%</t>
+          <t>2.70%→3.16%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
@@ -2654,7 +2654,7 @@
         <v>-7</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-51125200</v>
+        <v>-51923200</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
@@ -2677,11 +2677,11 @@
         <v>9</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>72435600</v>
+        <v>76266000</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>2.64%→2.90%</t>
+          <t>2.75%→3.01%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
@@ -2698,11 +2698,11 @@
         <v>-5</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-11552000</v>
+        <v>-11476000</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>2.96%→2.90%</t>
+          <t>2.91%→2.85%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
@@ -2721,11 +2721,11 @@
         <v>5</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>54682000</v>
+        <v>55480000</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>2.76%→2.95%</t>
+          <t>2.77%→2.96%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
@@ -2742,11 +2742,11 @@
         <v>-3</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-68514000</v>
+        <v>-71136000</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>1.72%→1.46%</t>
+          <t>1.77%→1.49%</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
@@ -2758,23 +2758,23 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>34412800</v>
+        <v>32224000</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>1.01%→1.13%</t>
+          <t>2.55%→2.66%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>31→35</t>
+          <t>85→89</t>
         </is>
       </c>
       <c r="G66" s="17" t="n"/>
@@ -2786,23 +2786,23 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>30552000</v>
+        <v>35142400</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>2.45%→2.55%</t>
+          <t>1.01%→1.14%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>85→89</t>
+          <t>31→35</t>
         </is>
       </c>
       <c r="G67" s="17" t="n"/>
@@ -2814,7 +2814,7 @@
     <row r="69" ht="19" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 470억   ·   현금 7억(1.4%)      오늘 2026-07-28  vs  5일전 2026-07-21      매수 4종목  /  매도 6종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 468억   ·   현금 7억(1.4%)      오늘 2026-07-28  vs  5일전 2026-07-21      매수 4종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B69" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260728.xlsx
+++ b/reports/pdf_rolling5_20260728.xlsx
@@ -1075,23 +1075,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-424972800</v>
+        <v>-372198400</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.52%</t>
+          <t>0.39%→0.27%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>56→42</t>
         </is>
       </c>
     </row>
@@ -1119,23 +1119,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-438860800</v>
+        <v>-424972800</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>1.03%→0.97%</t>
+          <t>0.58%→0.52%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>142→128</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
@@ -1163,23 +1163,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-372198400</v>
+        <v>-438860800</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.27%</t>
+          <t>1.03%→0.97%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>56→42</t>
+          <t>142→128</t>
         </is>
       </c>
     </row>
@@ -1395,23 +1395,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-743504000</v>
+        <v>-704816000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>1.20%→0.90%</t>
+          <t>9.05%→7.46%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>30→25</t>
+          <t>223→218</t>
         </is>
       </c>
     </row>
@@ -1423,23 +1423,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-704816000</v>
+        <v>-743504000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>9.05%→7.46%</t>
+          <t>1.20%→0.90%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>223→218</t>
+          <t>30→25</t>
         </is>
       </c>
     </row>
@@ -2559,23 +2559,23 @@
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-39459200</v>
+        <v>-35872000</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>1.12%→0.97%</t>
+          <t>0.63%→0.50%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>61→53</t>
+          <t>38→30</t>
         </is>
       </c>
     </row>
@@ -2603,23 +2603,23 @@
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-35872000</v>
+        <v>-39459200</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>0.63%→0.50%</t>
+          <t>1.12%→0.97%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>38→30</t>
+          <t>61→53</t>
         </is>
       </c>
     </row>
@@ -2758,23 +2758,23 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>32224000</v>
+        <v>35142400</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>2.55%→2.66%</t>
+          <t>1.01%→1.14%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>85→89</t>
+          <t>31→35</t>
         </is>
       </c>
       <c r="G66" s="17" t="n"/>
@@ -2786,23 +2786,23 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>35142400</v>
+        <v>32224000</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>1.01%→1.14%</t>
+          <t>2.55%→2.66%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>31→35</t>
+          <t>85→89</t>
         </is>
       </c>
       <c r="G67" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260728.xlsx
+++ b/reports/pdf_rolling5_20260728.xlsx
@@ -855,23 +855,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>코오롱생명과학  (편출)</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-23</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-908076800</v>
+        <v>-686761600</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>1.05%→0.94%</t>
+          <t>0.16%→0.00%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>121→98</t>
+          <t>23→0</t>
         </is>
       </c>
     </row>
@@ -899,23 +899,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>코오롱생명과학  (편출)</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-23</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-686761600</v>
+        <v>-908076800</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.16%→0.00%</t>
+          <t>1.05%→0.94%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>23→0</t>
+          <t>121→98</t>
         </is>
       </c>
     </row>
@@ -966,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>403545600</v>
+        <v>1098739200</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.68%→0.77%</t>
+          <t>3.97%→4.00%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>82→94</t>
+          <t>168→180</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1098739200</v>
+        <v>403545600</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>3.97%→4.00%</t>
+          <t>0.68%→0.77%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>168→180</t>
+          <t>82→94</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1295,23 +1295,23 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-351168000</v>
+        <v>-432115200</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>1.22%→1.05%</t>
+          <t>2.30%→2.31%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>138→132</t>
         </is>
       </c>
     </row>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-432115200</v>
+        <v>-351168000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>2.30%→2.31%</t>
+          <t>1.22%→1.05%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>138→132</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -1367,23 +1367,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-399776000</v>
+        <v>-743504000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.39%</t>
+          <t>1.20%→0.90%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>25→20</t>
+          <t>30→25</t>
         </is>
       </c>
     </row>
@@ -1423,23 +1423,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-743504000</v>
+        <v>-399776000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>1.20%→0.90%</t>
+          <t>0.44%→0.39%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>30→25</t>
+          <t>25→20</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260728.xlsx
+++ b/reports/pdf_rolling5_20260728.xlsx
@@ -966,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1098739200</v>
+        <v>390451200</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>3.97%→4.00%</t>
+          <t>0.52%→0.62%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>168→180</t>
+          <t>66→78</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1054,44 +1054,44 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>390451200</v>
+        <v>1098739200</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>0.52%→0.62%</t>
+          <t>3.97%→4.00%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>66→78</t>
+          <t>168→180</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-372198400</v>
+        <v>-424972800</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.27%</t>
+          <t>0.58%→0.52%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>56→42</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
@@ -1119,23 +1119,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-424972800</v>
+        <v>-438860800</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.52%</t>
+          <t>1.03%→0.97%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>142→128</t>
         </is>
       </c>
     </row>
@@ -1163,23 +1163,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-438860800</v>
+        <v>-372198400</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.03%→0.97%</t>
+          <t>0.39%→0.27%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>142→128</t>
+          <t>56→42</t>
         </is>
       </c>
     </row>
@@ -1295,23 +1295,23 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-432115200</v>
+        <v>-351168000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>2.30%→2.31%</t>
+          <t>1.22%→1.05%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>138→132</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-351168000</v>
+        <v>-432115200</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>1.22%→1.05%</t>
+          <t>2.30%→2.31%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>138→132</t>
         </is>
       </c>
     </row>
@@ -1367,23 +1367,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-743504000</v>
+        <v>-399776000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>1.20%→0.90%</t>
+          <t>0.44%→0.39%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>30→25</t>
+          <t>25→20</t>
         </is>
       </c>
     </row>
@@ -1395,23 +1395,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-704816000</v>
+        <v>-743504000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>9.05%→7.46%</t>
+          <t>1.20%→0.90%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>223→218</t>
+          <t>30→25</t>
         </is>
       </c>
     </row>
@@ -1423,23 +1423,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-399776000</v>
+        <v>-704816000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.39%</t>
+          <t>9.05%→7.46%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>25→20</t>
+          <t>223→218</t>
         </is>
       </c>
     </row>
@@ -2559,23 +2559,23 @@
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-35872000</v>
+        <v>-39459200</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>0.63%→0.50%</t>
+          <t>1.12%→0.97%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>38→30</t>
+          <t>61→53</t>
         </is>
       </c>
     </row>
@@ -2603,23 +2603,23 @@
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-39459200</v>
+        <v>-35872000</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>1.12%→0.97%</t>
+          <t>0.63%→0.50%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>61→53</t>
+          <t>38→30</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260728.xlsx
+++ b/reports/pdf_rolling5_20260728.xlsx
@@ -966,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>390451200</v>
+        <v>1098739200</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.52%→0.62%</t>
+          <t>3.97%→4.00%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>66→78</t>
+          <t>168→180</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1054,44 +1054,44 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1098739200</v>
+        <v>390451200</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>3.97%→4.00%</t>
+          <t>0.52%→0.62%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>168→180</t>
+          <t>66→78</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-424972800</v>
+        <v>-372198400</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.52%</t>
+          <t>0.39%→0.27%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>56→42</t>
         </is>
       </c>
     </row>
@@ -1119,23 +1119,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-438860800</v>
+        <v>-424972800</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>1.03%→0.97%</t>
+          <t>0.58%→0.52%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>142→128</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
@@ -1163,23 +1163,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-372198400</v>
+        <v>-438860800</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.27%</t>
+          <t>1.03%→0.97%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>56→42</t>
+          <t>142→128</t>
         </is>
       </c>
     </row>
@@ -1295,23 +1295,23 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-351168000</v>
+        <v>-432115200</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>1.22%→1.05%</t>
+          <t>2.30%→2.31%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>138→132</t>
         </is>
       </c>
     </row>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-432115200</v>
+        <v>-351168000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>2.30%→2.31%</t>
+          <t>1.22%→1.05%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>138→132</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -1367,23 +1367,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-399776000</v>
+        <v>-704816000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.39%</t>
+          <t>9.05%→7.46%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>25→20</t>
+          <t>223→218</t>
         </is>
       </c>
     </row>
@@ -1423,23 +1423,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-704816000</v>
+        <v>-399776000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>9.05%→7.46%</t>
+          <t>0.44%→0.39%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>223→218</t>
+          <t>25→20</t>
         </is>
       </c>
     </row>
@@ -2559,23 +2559,23 @@
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-39459200</v>
+        <v>-35872000</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>1.12%→0.97%</t>
+          <t>0.63%→0.50%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>61→53</t>
+          <t>38→30</t>
         </is>
       </c>
     </row>
@@ -2603,23 +2603,23 @@
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-35872000</v>
+        <v>-39459200</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>0.63%→0.50%</t>
+          <t>1.12%→0.97%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>38→30</t>
+          <t>61→53</t>
         </is>
       </c>
     </row>
@@ -2758,23 +2758,23 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>35142400</v>
+        <v>32224000</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>1.01%→1.14%</t>
+          <t>2.55%→2.66%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>31→35</t>
+          <t>85→89</t>
         </is>
       </c>
       <c r="G66" s="17" t="n"/>
@@ -2786,23 +2786,23 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>32224000</v>
+        <v>35142400</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>2.55%→2.66%</t>
+          <t>1.01%→1.14%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>85→89</t>
+          <t>31→35</t>
         </is>
       </c>
       <c r="G67" s="17" t="n"/>
